--- a/artfynd/A 54615-2022 artfynd.xlsx
+++ b/artfynd/A 54615-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136535844</v>
       </c>
       <c r="B2" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54615-2022 artfynd.xlsx
+++ b/artfynd/A 54615-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136535844</v>
       </c>
       <c r="B2" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54615-2022 artfynd.xlsx
+++ b/artfynd/A 54615-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136535844</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54615-2022 artfynd.xlsx
+++ b/artfynd/A 54615-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136535844</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54615-2022 artfynd.xlsx
+++ b/artfynd/A 54615-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136535844</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54615-2022 artfynd.xlsx
+++ b/artfynd/A 54615-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136535844</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54615-2022 artfynd.xlsx
+++ b/artfynd/A 54615-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136535844</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54615-2022 artfynd.xlsx
+++ b/artfynd/A 54615-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136535844</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54615-2022 artfynd.xlsx
+++ b/artfynd/A 54615-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136535844</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54615-2022 artfynd.xlsx
+++ b/artfynd/A 54615-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136535844</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54615-2022 artfynd.xlsx
+++ b/artfynd/A 54615-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136535844</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54615-2022 artfynd.xlsx
+++ b/artfynd/A 54615-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136535844</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54615-2022 artfynd.xlsx
+++ b/artfynd/A 54615-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136535844</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
